--- a/docs/ENGINE_WORDS.xlsx
+++ b/docs/ENGINE_WORDS.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -87,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -109,6 +113,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -489,114 +496,121 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>※ 2026-10-15 결정: 한글 번역본은 만들지 않기로 했습니다(영어 키워드 + 한글 설명 보기). 이 표는 나중에 한글 키워드 보기를 추가할 때 쓰기 위해 보관합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>노란색 칸이 직접 작성하는 칸입니다. 나머지는 참고용입니다.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>작성 방법</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1. '번역어' 칸(노란색)에 한글 단어를 적어 주세요. 정하기 어려우면 비워 두셔도 됩니다. 비운 단어는 '후보(참고)'를 보고 함께 정합니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2. '포함' 칸은 이 언어에 넣을지 여부입니다. ○ 넣음 / ✕ 제외 / △ 아직 미정. 제외로 둔 것도 필요하면 ○로 바꾸세요.</t>
+          <t>1. '번역어' 칸(노란색)에 한글 단어를 적어 주세요. 정하기 어려우면 비워 두셔도 됩니다. 비운 단어는 '후보(참고)'를 보고 함께 정합니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3. 표에 없는 단어를 추가하고 싶으면 맨 아래 행에 이어서 적어 주세요.</t>
+          <t>2. '포함' 칸은 이 언어에 넣을지 여부입니다. ○ 넣음 / ✕ 제외 / △ 아직 미정. 제외로 둔 것도 필요하면 ○로 바꾸세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>3. 표에 없는 단어를 추가하고 싶으면 맨 아래 행에 이어서 적어 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>4. '점검' 칸은 자동으로 표시됩니다. '중복!'은 같은 한글을 두 번 쓴 것이고, '띄어쓰기 불가'는 번역어에 공백이 있다는 뜻입니다.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>번역어를 정할 때의 원칙</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>• 영어 하나에 한글 하나만 대응합니다. 같은 뜻의 한글을 둘 이상 쓰지 않습니다. (되돌릴 때 어느 쪽인지 알 수 없기 때문)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• 띄어쓰기 없는 단어 하나로 합니다. (예: '아니면만약')</t>
+          <t>• 영어 하나에 한글 하나만 대응합니다. 같은 뜻의 한글을 둘 이상 쓰지 않습니다. (되돌릴 때 어느 쪽인지 알 수 없기 때문)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• 번역어는 예약어가 되어 제작자가 변수·함수 이름으로 쓸 수 없습니다. 그래서 변수 이름으로 흔히 쓸 법한 단어는 피하는 편이 좋습니다. '충돌 위험' 칸은 제 추측입니다.</t>
+          <t>• 띄어쓰기 없는 단어 하나로 합니다. (예: '아니면만약')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>• 한글 보기에서도 문장 구조는 파이썬을 따릅니다. 키워드가 앞에 옵니다. (예: 만약 조건:)</t>
+          <t>• 번역어는 예약어가 되어 제작자가 변수·함수 이름으로 쓸 수 없습니다. 그래서 변수 이름으로 흔히 쓸 법한 단어는 피하는 편이 좋습니다. '충돌 위험' 칸은 제 추측입니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>• 한글 보기에서도 문장 구조는 파이썬을 따릅니다. 키워드가 앞에 옵니다. (예: 만약 조건:)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>• 연산 기호(+ - * / == != &lt; &gt; &lt;= &gt;= 등)와 괄호, 콜론, 쉼표는 한글 보기에서도 그대로입니다.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>이 표에 없는 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>• 게임 명령어 이름(예: 단서를 주는 명령어)은 어떤 명령어가 필요한지 정한 뒤에 따로 정리합니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>• 게임 명령어 이름(예: 단서를 주는 명령어)은 어떤 명령어가 필요한지 정한 뒤에 따로 정리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>• 제작자가 직접 지은 변수·함수 이름은 쓴 그대로 보입니다. (영문 별칭 기능 없음)</t>
         </is>
